--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:39:17+00:00</t>
+    <t>2026-08-28T13:49:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T13:49:20+00:00</t>
+    <t>2026-08-28T14:00:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T14:00:29+00:00</t>
+    <t>2026-08-31T13:41:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T13:41:24+00:00</t>
+    <t>2026-09-02T03:14:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:14:53+00:00</t>
+    <t>2026-09-02T03:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T03:38:58+00:00</t>
+    <t>2026-09-02T04:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T04:00:55+00:00</t>
+    <t>2026-09-02T06:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:41:45+00:00</t>
+    <t>2026-09-02T06:59:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T06:59:28+00:00</t>
+    <t>2026-09-02T09:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T09:29:03+00:00</t>
+    <t>2026-09-02T14:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -270,7 +270,7 @@
 dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-de-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
   </si>
   <si>
-    <t>Messbefunde.Kopfumfang</t>
+    <t>Messbefunde.kopfumfang</t>
   </si>
   <si>
     <t>Observation.id</t>
@@ -1044,7 +1044,7 @@
 </t>
   </si>
   <si>
-    <t>Messbefunde.Kopfumfang.Datum</t>
+    <t>Messbefunde.kopfumfang.Datum</t>
   </si>
   <si>
     <t>Observation.issued</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4025" uniqueCount="547">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:14:40+00:00</t>
+    <t>2026-09-02T14:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -270,7 +270,7 @@
 dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-de-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
   </si>
   <si>
-    <t>Messbefunde.kopfumfang</t>
+    <t>koerperlicheUntersuchung.kopfumfang</t>
   </si>
   <si>
     <t>Observation.id</t>
@@ -958,7 +958,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>Patient</t>
+    <t>persoenlicheInfosIndexpatient</t>
   </si>
   <si>
     <t>Observation.focus</t>
@@ -1044,7 +1044,7 @@
 </t>
   </si>
   <si>
-    <t>Messbefunde.kopfumfang.Datum</t>
+    <t>koerperlicheUntersuchung.kopfumfang.datumKopfumfang</t>
   </si>
   <si>
     <t>Observation.issued</t>
@@ -1157,6 +1157,9 @@
   </si>
   <si>
     <t>Quantity.value</t>
+  </si>
+  <si>
+    <t>koerperlicheUntersuchung.kopfumfang.kopfumfang</t>
   </si>
   <si>
     <t>Observation.value[x]:valueQuantity.comparator</t>
@@ -9304,15 +9307,15 @@
         <v>93</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>83</v>
+        <v>359</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9338,22 +9341,22 @@
         <v>106</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>227</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q69" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="R69" t="s" s="2">
         <v>77</v>
@@ -9377,10 +9380,10 @@
         <v>168</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9398,7 +9401,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>75</v>
@@ -9418,10 +9421,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9447,16 +9450,16 @@
         <v>189</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N70" t="s" s="2">
         <v>227</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9505,7 +9508,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -9525,10 +9528,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9554,16 +9557,16 @@
         <v>100</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9573,7 +9576,7 @@
         <v>77</v>
       </c>
       <c r="S71" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="T71" t="s" s="2">
         <v>77</v>
@@ -9612,7 +9615,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>75</v>
@@ -9621,7 +9624,7 @@
         <v>85</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>93</v>
@@ -9632,10 +9635,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9661,16 +9664,16 @@
         <v>106</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -9699,7 +9702,7 @@
       </c>
       <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -9717,7 +9720,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>75</v>
@@ -9737,10 +9740,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9766,16 +9769,16 @@
         <v>173</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -9800,13 +9803,13 @@
         <v>77</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -9824,7 +9827,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>75</v>
@@ -9833,7 +9836,7 @@
         <v>85</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>93</v>
@@ -9844,14 +9847,14 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9873,16 +9876,16 @@
         <v>173</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -9907,13 +9910,13 @@
         <v>77</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>77</v>
@@ -9931,7 +9934,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>75</v>
@@ -9951,10 +9954,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9977,19 +9980,19 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -10038,7 +10041,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>75</v>
@@ -10058,10 +10061,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10087,13 +10090,13 @@
         <v>173</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10104,7 +10107,7 @@
         <v>77</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>77</v>
@@ -10122,10 +10125,10 @@
         <v>257</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10143,7 +10146,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>75</v>
@@ -10163,10 +10166,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10266,10 +10269,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10371,10 +10374,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10478,10 +10481,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10581,10 +10584,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10686,10 +10689,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10793,10 +10796,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10898,10 +10901,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11005,10 +11008,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11112,10 +11115,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11219,10 +11222,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11326,10 +11329,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11355,16 +11358,16 @@
         <v>173</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -11392,10 +11395,10 @@
         <v>257</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>77</v>
@@ -11413,7 +11416,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
@@ -11433,10 +11436,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11459,16 +11462,16 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11518,7 +11521,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -11538,10 +11541,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11564,16 +11567,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11623,7 +11626,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>75</v>
@@ -11643,10 +11646,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11669,19 +11672,19 @@
         <v>77</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11730,7 +11733,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>75</v>
@@ -11742,7 +11745,7 @@
         <v>92</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
@@ -11750,10 +11753,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11853,10 +11856,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11958,14 +11961,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -11987,10 +11990,10 @@
         <v>130</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N94" t="s" s="2">
         <v>133</v>
@@ -12045,7 +12048,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -12065,10 +12068,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12091,16 +12094,16 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12150,7 +12153,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
@@ -12159,10 +12162,10 @@
         <v>85</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>77</v>
@@ -12170,10 +12173,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12196,16 +12199,16 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12255,19 +12258,19 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
@@ -12275,10 +12278,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12304,16 +12307,16 @@
         <v>173</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -12341,10 +12344,10 @@
         <v>110</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>77</v>
@@ -12362,7 +12365,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>75</v>
@@ -12382,10 +12385,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12411,16 +12414,16 @@
         <v>173</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -12448,10 +12451,10 @@
         <v>257</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -12469,7 +12472,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>75</v>
@@ -12489,10 +12492,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12515,19 +12518,19 @@
         <v>77</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>77</v>
@@ -12576,7 +12579,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>75</v>
@@ -12588,7 +12591,7 @@
         <v>92</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>77</v>
@@ -12596,10 +12599,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12625,10 +12628,10 @@
         <v>189</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>227</v>
@@ -12681,7 +12684,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -12701,10 +12704,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12727,16 +12730,16 @@
         <v>86</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -12786,7 +12789,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -12806,10 +12809,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12832,16 +12835,16 @@
         <v>86</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -12891,7 +12894,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -12911,10 +12914,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12937,19 +12940,19 @@
         <v>86</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -12998,7 +13001,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>75</v>
@@ -13010,7 +13013,7 @@
         <v>92</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>77</v>
@@ -13018,10 +13021,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13121,10 +13124,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13226,14 +13229,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13255,10 +13258,10 @@
         <v>130</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>133</v>
@@ -13313,7 +13316,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>75</v>
@@ -13333,10 +13336,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13362,13 +13365,13 @@
         <v>173</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O107" t="s" s="2">
         <v>256</v>
@@ -13420,7 +13423,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>85</v>
@@ -13440,10 +13443,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13469,13 +13472,13 @@
         <v>336</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>338</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O108" t="s" s="2">
         <v>340</v>
@@ -13525,7 +13528,7 @@
         <v>136</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>75</v>
@@ -13545,10 +13548,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C109" t="s" s="2">
         <v>343</v>
@@ -13576,13 +13579,13 @@
         <v>344</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>338</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O109" t="s" s="2">
         <v>340</v>
@@ -13634,7 +13637,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>75</v>
@@ -13654,10 +13657,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13757,10 +13760,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13862,10 +13865,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13969,10 +13972,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13998,22 +14001,22 @@
         <v>106</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N113" t="s" s="2">
         <v>227</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q113" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="R113" t="s" s="2">
         <v>77</v>
@@ -14037,10 +14040,10 @@
         <v>168</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>77</v>
@@ -14058,7 +14061,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>75</v>
@@ -14078,10 +14081,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14107,16 +14110,16 @@
         <v>189</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N114" t="s" s="2">
         <v>227</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>77</v>
@@ -14165,7 +14168,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>75</v>
@@ -14185,10 +14188,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14214,16 +14217,16 @@
         <v>100</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>77</v>
@@ -14233,7 +14236,7 @@
         <v>77</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>77</v>
@@ -14272,7 +14275,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>75</v>
@@ -14281,7 +14284,7 @@
         <v>85</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>93</v>
@@ -14292,10 +14295,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14321,16 +14324,16 @@
         <v>106</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -14379,7 +14382,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>75</v>
@@ -14399,10 +14402,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14428,16 +14431,16 @@
         <v>173</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -14462,13 +14465,13 @@
         <v>77</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>77</v>
@@ -14486,7 +14489,7 @@
         <v>77</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>75</v>
@@ -14495,7 +14498,7 @@
         <v>85</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>93</v>
@@ -14506,14 +14509,14 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -14535,16 +14538,16 @@
         <v>173</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -14569,13 +14572,13 @@
         <v>77</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>77</v>
@@ -14593,7 +14596,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>75</v>
@@ -14613,10 +14616,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14642,16 +14645,16 @@
         <v>78</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -14700,7 +14703,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>75</v>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:43+00:00</t>
+    <t>2026-09-02T15:16:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:16:54+00:00</t>
+    <t>2026-09-02T16:13:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:13:05+00:00</t>
+    <t>2026-09-02T16:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:35:11+00:00</t>
+    <t>2026-09-02T16:52:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T16:52:58+00:00</t>
+    <t>2026-09-02T17:07:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:07:58+00:00</t>
+    <t>2026-09-02T17:34:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:34:23+00:00</t>
+    <t>2026-09-02T17:52:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T17:52:03+00:00</t>
+    <t>2026-09-02T18:22:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T18:22:51+00:00</t>
+    <t>2026-09-03T06:59:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:59:35+00:00</t>
+    <t>2026-09-03T07:17:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:17:59+00:00</t>
+    <t>2026-09-03T07:33:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:33:22+00:00</t>
+    <t>2026-09-03T09:08:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:08:22+00:00</t>
+    <t>2026-09-03T09:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:27:13+00:00</t>
+    <t>2026-09-03T09:44:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
+++ b/branches/migration/2026.0.1-template-v0.11.3/StructureDefinition-mii-pr-seltene-kopfumfang.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T09:44:41+00:00</t>
+    <t>2026-09-03T10:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
